--- a/Exc2/FURPS.xlsx
+++ b/Exc2/FURPS.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="EH3pNXlkkmbwB8wmDCHceVyUtn7+AC7Eu6qCKCD2eOo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="JRvbHTh1wueBR98jcizK+qTWQ7Z0A4LzQ5zUCtfiLtw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
   <si>
     <t>Код</t>
   </si>
@@ -126,9 +126,6 @@
     <t>F11</t>
   </si>
   <si>
-    <t>получение СМС-уведомления подтверждения ставки (АБС, сотрудник депозитов)</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
@@ -138,13 +135,7 @@
     <t>U01</t>
   </si>
   <si>
-    <t>придерживаться системы дизайна для приложений, которая принята в компании</t>
-  </si>
-  <si>
-    <t>U02</t>
-  </si>
-  <si>
-    <t>Пользователи при работе должны видеть привычные цвета и брендированные элементы</t>
+    <t>При реализации придерживаться системы дизайна для приложений, которая принята в компании</t>
   </si>
   <si>
     <t>R</t>
@@ -153,25 +144,10 @@
     <t>Надёжность (Reliability)</t>
   </si>
   <si>
-    <t>R01</t>
-  </si>
-  <si>
-    <t>все сервисы должны работать 24/7</t>
-  </si>
-  <si>
     <t>R02</t>
   </si>
   <si>
-    <t>доступны в 99,9%</t>
-  </si>
-  <si>
-    <t>R03</t>
-  </si>
-  <si>
-    <t>равномерное горизонтальное масштабирование и распределение запросов между серверами, приложениями и ЦОД</t>
-  </si>
-  <si>
-    <t>R04</t>
+    <t>Доступность сервисов 99,9%</t>
   </si>
   <si>
     <t>P</t>
@@ -180,13 +156,10 @@
     <t>Производительность (Performance)</t>
   </si>
   <si>
-    <t>P1</t>
+    <t>P01</t>
   </si>
   <si>
-    <t>Отклик по всем операциям быстрый - миллисекунды</t>
-  </si>
-  <si>
-    <t>...</t>
+    <t>Время отклика по всем операциям порядка миллисекунд</t>
   </si>
   <si>
     <t>S</t>
@@ -198,7 +171,7 @@
     <t>S01</t>
   </si>
   <si>
-    <t>как можно больше использовать технологии, которые уже есть в банке (базы данных MS SQL и Oracle)</t>
+    <t>использовать технологии, которые уже есть в банке (базы данных MS SQL и Oracle)</t>
   </si>
   <si>
     <t>S02</t>
@@ -244,6 +217,12 @@
   </si>
   <si>
     <t>предусмотреть разработку документации для дальнейшего расширения системы</t>
+  </si>
+  <si>
+    <t>+R05</t>
+  </si>
+  <si>
+    <t>Исключить прямую интеграцию интернет-банка с API АБС</t>
   </si>
 </sst>
 </file>
@@ -372,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -408,9 +387,6 @@
     </xf>
     <xf borderId="2" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf quotePrefix="1" borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1166,10 +1142,14 @@
         <v>35</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="F15" s="10"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1227,10 +1207,10 @@
     <row r="17" ht="30.0" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1261,10 +1241,10 @@
     <row r="18" ht="30.0" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
@@ -1294,15 +1274,15 @@
     </row>
     <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1328,15 +1308,15 @@
     </row>
     <row r="20" ht="30.0" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1362,15 +1342,15 @@
     </row>
     <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1397,10 +1377,10 @@
     <row r="22" ht="30.0" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -1430,15 +1410,15 @@
     </row>
     <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1462,12 +1442,14 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" ht="30.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="12"/>
@@ -1496,15 +1478,15 @@
     </row>
     <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="12"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1533,11 +1515,11 @@
       <c r="B26" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
       <c r="F26" s="12"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1564,13 +1546,15 @@
     </row>
     <row r="27" ht="30.0" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="12"/>
+      <c r="C27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1594,17 +1578,19 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" ht="30.0" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="5" t="s">
+    <row r="28">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="7"/>
+      <c r="C28" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1628,16 +1614,16 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29">
-      <c r="A29" s="1"/>
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="14"/>
       <c r="B29" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>60</v>
+      <c r="C29" s="9" t="s">
+        <v>62</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="12"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1662,17 +1648,17 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" ht="30.0" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="12"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1696,17 +1682,17 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" ht="30.0" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="12"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1730,17 +1716,17 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" ht="30.0" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="4" t="s">
-        <v>65</v>
+      <c r="B32" s="8" t="s">
+        <v>67</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>66</v>
+      <c r="C32" s="9" t="s">
+        <v>68</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1764,19 +1750,13 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
-        <v>69</v>
-      </c>
+    <row r="33" ht="12.75" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1800,17 +1780,13 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" ht="33.0" customHeight="1">
-      <c r="A34" s="15"/>
-      <c r="B34" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="12"/>
+    <row r="34" ht="12.75" customHeight="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1836,14 +1812,10 @@
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1870,14 +1842,10 @@
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -31092,164 +31060,14 @@
       <c r="AA1009" s="1"/>
       <c r="AB1009" s="1"/>
     </row>
-    <row r="1010" ht="12.75" customHeight="1">
-      <c r="A1010" s="1"/>
-      <c r="B1010" s="1"/>
-      <c r="C1010" s="1"/>
-      <c r="D1010" s="1"/>
-      <c r="E1010" s="1"/>
-      <c r="F1010" s="1"/>
-      <c r="G1010" s="1"/>
-      <c r="H1010" s="1"/>
-      <c r="I1010" s="1"/>
-      <c r="J1010" s="1"/>
-      <c r="K1010" s="1"/>
-      <c r="L1010" s="1"/>
-      <c r="M1010" s="1"/>
-      <c r="N1010" s="1"/>
-      <c r="O1010" s="1"/>
-      <c r="P1010" s="1"/>
-      <c r="Q1010" s="1"/>
-      <c r="R1010" s="1"/>
-      <c r="S1010" s="1"/>
-      <c r="T1010" s="1"/>
-      <c r="U1010" s="1"/>
-      <c r="V1010" s="1"/>
-      <c r="W1010" s="1"/>
-      <c r="X1010" s="1"/>
-      <c r="Y1010" s="1"/>
-      <c r="Z1010" s="1"/>
-      <c r="AA1010" s="1"/>
-      <c r="AB1010" s="1"/>
-    </row>
-    <row r="1011" ht="12.75" customHeight="1">
-      <c r="A1011" s="1"/>
-      <c r="B1011" s="1"/>
-      <c r="C1011" s="1"/>
-      <c r="D1011" s="1"/>
-      <c r="E1011" s="1"/>
-      <c r="F1011" s="1"/>
-      <c r="G1011" s="1"/>
-      <c r="H1011" s="1"/>
-      <c r="I1011" s="1"/>
-      <c r="J1011" s="1"/>
-      <c r="K1011" s="1"/>
-      <c r="L1011" s="1"/>
-      <c r="M1011" s="1"/>
-      <c r="N1011" s="1"/>
-      <c r="O1011" s="1"/>
-      <c r="P1011" s="1"/>
-      <c r="Q1011" s="1"/>
-      <c r="R1011" s="1"/>
-      <c r="S1011" s="1"/>
-      <c r="T1011" s="1"/>
-      <c r="U1011" s="1"/>
-      <c r="V1011" s="1"/>
-      <c r="W1011" s="1"/>
-      <c r="X1011" s="1"/>
-      <c r="Y1011" s="1"/>
-      <c r="Z1011" s="1"/>
-      <c r="AA1011" s="1"/>
-      <c r="AB1011" s="1"/>
-    </row>
-    <row r="1012" ht="12.75" customHeight="1">
-      <c r="A1012" s="1"/>
-      <c r="B1012" s="1"/>
-      <c r="C1012" s="1"/>
-      <c r="D1012" s="1"/>
-      <c r="E1012" s="1"/>
-      <c r="F1012" s="1"/>
-      <c r="G1012" s="1"/>
-      <c r="H1012" s="1"/>
-      <c r="I1012" s="1"/>
-      <c r="J1012" s="1"/>
-      <c r="K1012" s="1"/>
-      <c r="L1012" s="1"/>
-      <c r="M1012" s="1"/>
-      <c r="N1012" s="1"/>
-      <c r="O1012" s="1"/>
-      <c r="P1012" s="1"/>
-      <c r="Q1012" s="1"/>
-      <c r="R1012" s="1"/>
-      <c r="S1012" s="1"/>
-      <c r="T1012" s="1"/>
-      <c r="U1012" s="1"/>
-      <c r="V1012" s="1"/>
-      <c r="W1012" s="1"/>
-      <c r="X1012" s="1"/>
-      <c r="Y1012" s="1"/>
-      <c r="Z1012" s="1"/>
-      <c r="AA1012" s="1"/>
-      <c r="AB1012" s="1"/>
-    </row>
-    <row r="1013" ht="12.75" customHeight="1">
-      <c r="A1013" s="1"/>
-      <c r="B1013" s="1"/>
-      <c r="C1013" s="1"/>
-      <c r="D1013" s="1"/>
-      <c r="E1013" s="1"/>
-      <c r="F1013" s="1"/>
-      <c r="G1013" s="1"/>
-      <c r="H1013" s="1"/>
-      <c r="I1013" s="1"/>
-      <c r="J1013" s="1"/>
-      <c r="K1013" s="1"/>
-      <c r="L1013" s="1"/>
-      <c r="M1013" s="1"/>
-      <c r="N1013" s="1"/>
-      <c r="O1013" s="1"/>
-      <c r="P1013" s="1"/>
-      <c r="Q1013" s="1"/>
-      <c r="R1013" s="1"/>
-      <c r="S1013" s="1"/>
-      <c r="T1013" s="1"/>
-      <c r="U1013" s="1"/>
-      <c r="V1013" s="1"/>
-      <c r="W1013" s="1"/>
-      <c r="X1013" s="1"/>
-      <c r="Y1013" s="1"/>
-      <c r="Z1013" s="1"/>
-      <c r="AA1013" s="1"/>
-      <c r="AB1013" s="1"/>
-    </row>
-    <row r="1014" ht="12.75" customHeight="1">
-      <c r="A1014" s="1"/>
-      <c r="B1014" s="1"/>
-      <c r="C1014" s="1"/>
-      <c r="D1014" s="1"/>
-      <c r="E1014" s="1"/>
-      <c r="F1014" s="1"/>
-      <c r="G1014" s="1"/>
-      <c r="H1014" s="1"/>
-      <c r="I1014" s="1"/>
-      <c r="J1014" s="1"/>
-      <c r="K1014" s="1"/>
-      <c r="L1014" s="1"/>
-      <c r="M1014" s="1"/>
-      <c r="N1014" s="1"/>
-      <c r="O1014" s="1"/>
-      <c r="P1014" s="1"/>
-      <c r="Q1014" s="1"/>
-      <c r="R1014" s="1"/>
-      <c r="S1014" s="1"/>
-      <c r="T1014" s="1"/>
-      <c r="U1014" s="1"/>
-      <c r="V1014" s="1"/>
-      <c r="W1014" s="1"/>
-      <c r="X1014" s="1"/>
-      <c r="Y1014" s="1"/>
-      <c r="Z1014" s="1"/>
-      <c r="AA1014" s="1"/>
-      <c r="AB1014" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/Exc2/FURPS.xlsx
+++ b/Exc2/FURPS.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="JRvbHTh1wueBR98jcizK+qTWQ7Z0A4LzQ5zUCtfiLtw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="g0tpa2/rjjk7iKx5i8kd0Z6hT4MyXprF4krTR5SpQ7E="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
   <si>
     <t>Код</t>
   </si>
@@ -96,7 +96,7 @@
     <t>F07</t>
   </si>
   <si>
-    <t>Просмотреть заявки</t>
+    <t>Изучить заявку</t>
   </si>
   <si>
     <t>Система кол-центра</t>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>F08</t>
+  </si>
+  <si>
+    <t>Получить новые заявки</t>
   </si>
   <si>
     <t>F09</t>
@@ -124,6 +127,9 @@
   </si>
   <si>
     <t>F11</t>
+  </si>
+  <si>
+    <t>Получить доступные депозиты</t>
   </si>
   <si>
     <t>U</t>
@@ -1028,13 +1034,13 @@
         <v>29</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="1"/>
@@ -1063,16 +1069,16 @@
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="1"/>
@@ -1101,16 +1107,16 @@
     <row r="14" ht="30.0" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="1"/>
@@ -1136,19 +1142,19 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30.0" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="1"/>
@@ -1176,11 +1182,15 @@
     </row>
     <row r="16" ht="30.0" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1206,15 +1216,15 @@
     </row>
     <row r="17" ht="30.0" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="4" t="s">
-        <v>36</v>
+      <c r="B17" s="8" t="s">
+        <v>40</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>37</v>
+      <c r="C17" s="11" t="s">
+        <v>41</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="12"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1240,15 +1250,15 @@
     </row>
     <row r="18" ht="30.0" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="8" t="s">
-        <v>38</v>
+      <c r="B18" s="4" t="s">
+        <v>42</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>39</v>
+      <c r="C18" s="13" t="s">
+        <v>43</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1274,15 +1284,15 @@
     </row>
     <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="4" t="s">
-        <v>40</v>
+      <c r="B19" s="8" t="s">
+        <v>44</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>41</v>
+      <c r="C19" s="11" t="s">
+        <v>45</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1308,15 +1318,15 @@
     </row>
     <row r="20" ht="30.0" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="8" t="s">
-        <v>42</v>
+      <c r="B20" s="4" t="s">
+        <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>43</v>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1342,15 +1352,15 @@
     </row>
     <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="4" t="s">
-        <v>44</v>
+      <c r="B21" s="8" t="s">
+        <v>48</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>45</v>
+      <c r="C21" s="11" t="s">
+        <v>49</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1376,15 +1386,15 @@
     </row>
     <row r="22" ht="30.0" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="8" t="s">
-        <v>46</v>
+      <c r="B22" s="4" t="s">
+        <v>50</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>47</v>
+      <c r="C22" s="5" t="s">
+        <v>51</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1408,17 +1418,17 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" ht="30.0" customHeight="1">
+    <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="4" t="s">
-        <v>48</v>
+      <c r="B23" s="8" t="s">
+        <v>52</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>49</v>
+      <c r="C23" s="11" t="s">
+        <v>53</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="7"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1442,16 +1452,16 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30.0" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>51</v>
+      <c r="C24" s="9" t="s">
+        <v>55</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="12"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1479,10 +1489,10 @@
     <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -1512,15 +1522,15 @@
     </row>
     <row r="26" ht="30.0" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="8" t="s">
-        <v>54</v>
+      <c r="B26" s="4" t="s">
+        <v>58</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>55</v>
+      <c r="C26" s="5" t="s">
+        <v>59</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="12"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1544,17 +1554,19 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" ht="30.0" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="4" t="s">
-        <v>56</v>
+    <row r="27">
+      <c r="A27" s="14"/>
+      <c r="B27" s="15" t="s">
+        <v>60</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>57</v>
+      <c r="C27" s="9" t="s">
+        <v>61</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="7"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1578,19 +1590,17 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" ht="33.0" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="15" t="s">
-        <v>58</v>
+      <c r="B28" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9" t="s">
-        <v>60</v>
-      </c>
+      <c r="F28" s="12"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1614,17 +1624,17 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" ht="33.0" customHeight="1">
-      <c r="A29" s="14"/>
+    <row r="29" ht="12.75" customHeight="1">
+      <c r="A29" s="1"/>
       <c r="B29" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="12"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1651,10 +1661,10 @@
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -1685,13 +1695,13 @@
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -1718,12 +1728,8 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -31030,44 +31036,14 @@
       <c r="AA1008" s="1"/>
       <c r="AB1008" s="1"/>
     </row>
-    <row r="1009" ht="12.75" customHeight="1">
-      <c r="A1009" s="1"/>
-      <c r="B1009" s="1"/>
-      <c r="C1009" s="1"/>
-      <c r="D1009" s="1"/>
-      <c r="E1009" s="1"/>
-      <c r="F1009" s="1"/>
-      <c r="G1009" s="1"/>
-      <c r="H1009" s="1"/>
-      <c r="I1009" s="1"/>
-      <c r="J1009" s="1"/>
-      <c r="K1009" s="1"/>
-      <c r="L1009" s="1"/>
-      <c r="M1009" s="1"/>
-      <c r="N1009" s="1"/>
-      <c r="O1009" s="1"/>
-      <c r="P1009" s="1"/>
-      <c r="Q1009" s="1"/>
-      <c r="R1009" s="1"/>
-      <c r="S1009" s="1"/>
-      <c r="T1009" s="1"/>
-      <c r="U1009" s="1"/>
-      <c r="V1009" s="1"/>
-      <c r="W1009" s="1"/>
-      <c r="X1009" s="1"/>
-      <c r="Y1009" s="1"/>
-      <c r="Z1009" s="1"/>
-      <c r="AA1009" s="1"/>
-      <c r="AB1009" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/Exc2/FURPS.xlsx
+++ b/Exc2/FURPS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>Код</t>
   </si>
@@ -108,7 +108,7 @@
     <t>F08</t>
   </si>
   <si>
-    <t>Получить новые заявки</t>
+    <t>Получить заявки</t>
   </si>
   <si>
     <t>F09</t>
@@ -123,13 +123,22 @@
     <t>F10</t>
   </si>
   <si>
-    <t>Подтвердить условия депозита</t>
+    <t>Обработать заявку</t>
   </si>
   <si>
     <t>F11</t>
   </si>
   <si>
     <t>Получить доступные депозиты</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>Подтвердить личности клиента</t>
+  </si>
+  <si>
+    <t>Сотрудник отделения</t>
   </si>
   <si>
     <t>U</t>
@@ -150,7 +159,7 @@
     <t>Надёжность (Reliability)</t>
   </si>
   <si>
-    <t>R02</t>
+    <t>R01</t>
   </si>
   <si>
     <t>Доступность сервисов 99,9%</t>
@@ -177,19 +186,19 @@
     <t>S01</t>
   </si>
   <si>
-    <t>использовать технологии, которые уже есть в банке (базы данных MS SQL и Oracle)</t>
+    <t>Использовать технологии, которые уже применены</t>
   </si>
   <si>
     <t>S02</t>
   </si>
   <si>
-    <t>новые технологии должны быть совместимы с существующими платформами разработки</t>
+    <t>Новые технологии должны быть совместимы с существующими платформами разработки</t>
   </si>
   <si>
     <t>S03</t>
   </si>
   <si>
-    <t>сотрудники понимали новые технологии хотя бы на уровне языков программирования</t>
+    <t>Технологии должны быть понятны сотрудникам хотя бы на уровне языков программирования</t>
   </si>
   <si>
     <t>+R</t>
@@ -210,22 +219,16 @@
     <t>+R02</t>
   </si>
   <si>
-    <t>для АБС доступно только вертикальное масштабирование</t>
+    <t>Только вертикальное масштабирование</t>
   </si>
   <si>
     <t>+R03</t>
   </si>
   <si>
-    <t xml:space="preserve">текущая версия платформы интернет-банка несовместима с Kafka </t>
+    <t xml:space="preserve">Несовместимость с Kafka </t>
   </si>
   <si>
     <t>+R04</t>
-  </si>
-  <si>
-    <t>предусмотреть разработку документации для дальнейшего расширения системы</t>
-  </si>
-  <si>
-    <t>+R05</t>
   </si>
   <si>
     <t>Исключить прямую интеграцию интернет-банка с API АБС</t>
@@ -1182,15 +1185,19 @@
     </row>
     <row r="16" ht="30.0" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7"/>
+      <c r="D16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="10"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1216,15 +1223,15 @@
     </row>
     <row r="17" ht="30.0" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
+      <c r="C17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1250,15 +1257,15 @@
     </row>
     <row r="18" ht="30.0" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1284,15 +1291,15 @@
     </row>
     <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
+      <c r="C19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1318,15 +1325,15 @@
     </row>
     <row r="20" ht="30.0" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
+      <c r="C20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1352,15 +1359,15 @@
     </row>
     <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="B21" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
+      <c r="C21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1386,15 +1393,15 @@
     </row>
     <row r="22" ht="30.0" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1418,17 +1425,17 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="B23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
+      <c r="C23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1452,16 +1459,16 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" ht="30.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="C24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="12"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1489,10 +1496,10 @@
     <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -1522,15 +1529,15 @@
     </row>
     <row r="26" ht="30.0" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
+      <c r="C26" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1554,19 +1561,17 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="9" t="s">
+    <row r="27" ht="30.0" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9" t="s">
+      <c r="C27" s="5" t="s">
         <v>62</v>
       </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1590,9 +1595,9 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" ht="33.0" customHeight="1">
+    <row r="28">
       <c r="A28" s="14"/>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="9" t="s">
@@ -1600,7 +1605,9 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1624,17 +1631,19 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="1"/>
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="14"/>
       <c r="B29" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="1"/>
+      <c r="D29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="12"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1661,12 +1670,14 @@
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
-      <c r="D30" s="11"/>
+      <c r="D30" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="E30" s="11"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1694,13 +1705,15 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="8" t="s">
-        <v>69</v>
+      <c r="B31" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -31039,11 +31052,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
